--- a/research/power_model_scenarios_2026-06-23.xlsx
+++ b/research/power_model_scenarios_2026-06-23.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FLOPs Basis (ITEM 8)" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retirement 0.20 (ITEM 9)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FLOPs + Retire 0.20" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tokens to FLOPs to Power" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3542,4 +3543,469 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>tokens_per_day_T</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>avg_N_active_B</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FLOPs_per_token</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>FLOPs_per_day</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>fleet_TFLOP_per_W</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>power_GW</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B2" t="n">
+        <v>134.9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>297</v>
+      </c>
+      <c r="D2" t="n">
+        <v>594400000000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8.019775568e+25</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G2" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B3" t="n">
+        <v>460.8</v>
+      </c>
+      <c r="C3" t="n">
+        <v>284</v>
+      </c>
+      <c r="D3" t="n">
+        <v>568573333333.3335</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.620236234410001e+26</v>
+      </c>
+      <c r="F3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G3" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B4" t="n">
+        <v>763.6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>271</v>
+      </c>
+      <c r="D4" t="n">
+        <v>542746666666.6667</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.144485603749434e+26</v>
+      </c>
+      <c r="F4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G4" t="n">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1359.8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>258</v>
+      </c>
+      <c r="D5" t="n">
+        <v>516920000000.0001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7.029092283445739e+26</v>
+      </c>
+      <c r="F5" t="n">
+        <v>18</v>
+      </c>
+      <c r="G5" t="n">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2172.8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>246</v>
+      </c>
+      <c r="D6" t="n">
+        <v>491093333333.3334</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.067044527201479e+27</v>
+      </c>
+      <c r="F6" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3253.6</v>
+      </c>
+      <c r="C7" t="n">
+        <v>233</v>
+      </c>
+      <c r="D7" t="n">
+        <v>465266666666.6667</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.513784217271805e+27</v>
+      </c>
+      <c r="F7" t="n">
+        <v>25</v>
+      </c>
+      <c r="G7" t="n">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4573</v>
+      </c>
+      <c r="C8" t="n">
+        <v>220</v>
+      </c>
+      <c r="D8" t="n">
+        <v>439440000000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.009575561527522e+27</v>
+      </c>
+      <c r="F8" t="n">
+        <v>28</v>
+      </c>
+      <c r="G8" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5901.4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>207</v>
+      </c>
+      <c r="D9" t="n">
+        <v>413613333333.3334</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.440904972563264e+27</v>
+      </c>
+      <c r="F9" t="n">
+        <v>31</v>
+      </c>
+      <c r="G9" t="n">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B10" t="n">
+        <v>7334.6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>194</v>
+      </c>
+      <c r="D10" t="n">
+        <v>387786666666.6667</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.844266253508487e+27</v>
+      </c>
+      <c r="F10" t="n">
+        <v>34</v>
+      </c>
+      <c r="G10" t="n">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2034</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8998.700000000001</v>
+      </c>
+      <c r="C11" t="n">
+        <v>181</v>
+      </c>
+      <c r="D11" t="n">
+        <v>361960000000.0001</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.257171657445915e+27</v>
+      </c>
+      <c r="F11" t="n">
+        <v>37</v>
+      </c>
+      <c r="G11" t="n">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2035</v>
+      </c>
+      <c r="B12" t="n">
+        <v>10620.4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>168</v>
+      </c>
+      <c r="D12" t="n">
+        <v>336133333333.3334</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.569885801726098e+27</v>
+      </c>
+      <c r="F12" t="n">
+        <v>40</v>
+      </c>
+      <c r="G12" t="n">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2036</v>
+      </c>
+      <c r="B13" t="n">
+        <v>12433.3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>155</v>
+      </c>
+      <c r="D13" t="n">
+        <v>310306666666.6667</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.858127564796659e+27</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="G13" t="n">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B14" t="n">
+        <v>14482.7</v>
+      </c>
+      <c r="C14" t="n">
+        <v>142</v>
+      </c>
+      <c r="D14" t="n">
+        <v>284480000000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.120045026395084e+27</v>
+      </c>
+      <c r="F14" t="n">
+        <v>45.71428571428572</v>
+      </c>
+      <c r="G14" t="n">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B15" t="n">
+        <v>16709.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>129</v>
+      </c>
+      <c r="D15" t="n">
+        <v>258653333333.3334</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4.321872856006917e+27</v>
+      </c>
+      <c r="F15" t="n">
+        <v>48.57142857142857</v>
+      </c>
+      <c r="G15" t="n">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2039</v>
+      </c>
+      <c r="B16" t="n">
+        <v>18373.4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>116</v>
+      </c>
+      <c r="D16" t="n">
+        <v>232826666666.6667</v>
+      </c>
+      <c r="E16" t="n">
+        <v>4.277827989502399e+27</v>
+      </c>
+      <c r="F16" t="n">
+        <v>51.42857142857143</v>
+      </c>
+      <c r="G16" t="n">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2040</v>
+      </c>
+      <c r="B17" t="n">
+        <v>20019.8</v>
+      </c>
+      <c r="C17" t="n">
+        <v>104</v>
+      </c>
+      <c r="D17" t="n">
+        <v>207000000000</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.144100890949015e+27</v>
+      </c>
+      <c r="F17" t="n">
+        <v>54.28571428571428</v>
+      </c>
+      <c r="G17" t="n">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2041</v>
+      </c>
+      <c r="B18" t="n">
+        <v>21860.1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>104</v>
+      </c>
+      <c r="D18" t="n">
+        <v>207000000000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4.525045654881313e+27</v>
+      </c>
+      <c r="F18" t="n">
+        <v>57.14285714285714</v>
+      </c>
+      <c r="G18" t="n">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2042</v>
+      </c>
+      <c r="B19" t="n">
+        <v>23789.7</v>
+      </c>
+      <c r="C19" t="n">
+        <v>104</v>
+      </c>
+      <c r="D19" t="n">
+        <v>207000000000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4.924465552656274e+27</v>
+      </c>
+      <c r="F19" t="n">
+        <v>60</v>
+      </c>
+      <c r="G19" t="n">
+        <v>708</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>